--- a/data/trans_bre/P16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; -1,06</t>
+          <t>-5,48; -0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,15</t>
+          <t>-6,07; -1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,61</t>
+          <t>-3,76; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,08</t>
+          <t>-3,6; 1,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,09; -13,88</t>
+          <t>-52,77; -12,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,5; -11,44</t>
+          <t>-46,94; -12,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,38; 24,23</t>
+          <t>-39,93; 20,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 30,38</t>
+          <t>-33,45; 28,85</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,94</t>
+          <t>-1,35; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 2,36</t>
+          <t>-1,69; 2,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,88</t>
+          <t>-0,64; 2,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 3,69</t>
+          <t>-1,18; 3,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 40,36</t>
+          <t>-20,36; 43,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 32,12</t>
+          <t>-17,67; 30,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 42,51</t>
+          <t>-7,48; 41,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 83,34</t>
+          <t>-15,23; 76,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 6,31</t>
+          <t>-0,57; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 1,69</t>
+          <t>-6,06; 1,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 4,47</t>
+          <t>-2,36; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 1,5</t>
+          <t>-4,85; 1,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 128,42</t>
+          <t>-9,17; 131,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 23,32</t>
+          <t>-49,87; 28,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 83,23</t>
+          <t>-25,21; 73,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,02; 25,14</t>
+          <t>-44,95; 18,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,73</t>
+          <t>-1,73; 0,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,23</t>
+          <t>-2,59; 0,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,97</t>
+          <t>-0,77; 1,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,1</t>
+          <t>-1,04; 2,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 11,55</t>
+          <t>-23,63; 10,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 2,74</t>
+          <t>-24,84; 2,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 27,66</t>
+          <t>-9,23; 27,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 37,92</t>
+          <t>-13,64; 41,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,48; -0,95</t>
+          <t>-5,55; -1,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,23</t>
+          <t>-6,19; -1,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 1,44</t>
+          <t>-3,8; 1,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,95</t>
+          <t>-2,46; 2,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-52,77; -12,32</t>
+          <t>-52,39; -15,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,94; -12,22</t>
+          <t>-48,82; -12,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,93; 20,61</t>
+          <t>-39,03; 22,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,45; 28,85</t>
+          <t>-24,76; 41,14</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,17</t>
+          <t>-1,28; 1,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,34</t>
+          <t>-1,59; 2,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,85</t>
+          <t>-0,72; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,3</t>
+          <t>-0,43; 2,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 43,68</t>
+          <t>-20,69; 36,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 30,94</t>
+          <t>-17,13; 32,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 41,51</t>
+          <t>-8,94; 41,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,23; 76,96</t>
+          <t>-6,18; 47,14</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,04%</t>
+          <t>-13,61%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 6,51</t>
+          <t>-0,39; 6,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 1,97</t>
+          <t>-6,68; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,19</t>
+          <t>-2,09; 4,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,25</t>
+          <t>-4,85; 1,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 131,7</t>
+          <t>-4,54; 138,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,87; 28,02</t>
+          <t>-52,48; 24,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-25,21; 73,91</t>
+          <t>-23,58; 80,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 18,09</t>
+          <t>-43,35; 21,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,7</t>
+          <t>-1,73; 0,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,23</t>
+          <t>-2,47; 0,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,9</t>
+          <t>-0,69; 1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,35</t>
+          <t>-0,78; 1,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 10,64</t>
+          <t>-22,35; 11,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 2,99</t>
+          <t>-24,42; 4,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 27,06</t>
+          <t>-7,95; 27,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,64; 41,78</t>
+          <t>-10,05; 26,41</t>
         </is>
       </c>
     </row>
